--- a/Utility/Security Desgin/Security Boundaries Table.xlsx
+++ b/Utility/Security Desgin/Security Boundaries Table.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">[GET]         api/V1/Fines/{id}</t>
   </si>
   <si>
-    <t xml:space="preserve">[GET]         api/V1/Fines/Report</t>
+    <t xml:space="preserve">[GET]         api/V1/Fines/Users/{UserId}/Report</t>
   </si>
   <si>
     <t xml:space="preserve">[PUT]         api/V1/BorrowingRecords/{id}/{NewDate}</t>
@@ -124,7 +124,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -143,8 +143,14 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11.000000"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -166,13 +172,34 @@
     <fill>
       <patternFill patternType="none"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="47"/>
+        <bgColor indexed="47"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left style="none"/>
       <right style="none"/>
       <top style="none"/>
       <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -193,31 +220,51 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="2" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
     <xf fontId="2" fillId="3" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
     <xf fontId="0" fillId="4" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
     <xf fontId="0" fillId="4" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf fontId="3" fillId="5" borderId="1" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf fontId="1" fillId="2" borderId="2" numFmtId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf fontId="1" fillId="2" borderId="3" numFmtId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="2" borderId="4" numFmtId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="3" fillId="5" borderId="1" numFmtId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Accent5" xfId="2" builtinId="45"/>
     <cellStyle name="Currency" xfId="3" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Input" xfId="5" builtinId="20"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -745,6 +792,7 @@
       <c r="B2" t="s">
         <v>3</v>
       </c>
+      <c r="C2" s="4"/>
     </row>
     <row r="3" ht="14.25">
       <c r="A3" s="3" t="s">
@@ -753,6 +801,7 @@
       <c r="B3" t="s">
         <v>5</v>
       </c>
+      <c r="C3" s="4"/>
     </row>
     <row r="4" ht="14.25">
       <c r="A4" s="3" t="s">
@@ -761,6 +810,7 @@
       <c r="B4" t="s">
         <v>3</v>
       </c>
+      <c r="C4" s="4"/>
     </row>
     <row r="5" ht="14.25">
       <c r="A5" s="3" t="s">
@@ -769,6 +819,7 @@
       <c r="B5" t="s">
         <v>3</v>
       </c>
+      <c r="C5" s="4"/>
     </row>
     <row r="6" ht="14.25">
       <c r="A6" s="3" t="s">
@@ -777,6 +828,7 @@
       <c r="B6" t="s">
         <v>5</v>
       </c>
+      <c r="C6" s="4"/>
     </row>
     <row r="7" ht="14.25">
       <c r="A7" s="3" t="s">
@@ -785,6 +837,7 @@
       <c r="B7" t="s">
         <v>5</v>
       </c>
+      <c r="C7" s="4"/>
     </row>
     <row r="8" ht="14.25">
       <c r="A8" s="3" t="s">
@@ -793,6 +846,7 @@
       <c r="B8" t="s">
         <v>11</v>
       </c>
+      <c r="C8" s="5"/>
     </row>
     <row r="9" ht="14.25">
       <c r="A9" s="3" t="s">
@@ -801,6 +855,7 @@
       <c r="B9" t="s">
         <v>11</v>
       </c>
+      <c r="C9" s="5"/>
     </row>
     <row r="10" ht="14.25">
       <c r="A10" s="3" t="s">
@@ -809,6 +864,7 @@
       <c r="B10" t="s">
         <v>11</v>
       </c>
+      <c r="C10" s="5"/>
     </row>
     <row r="11" ht="14.25">
       <c r="A11" s="3" t="s">
@@ -817,6 +873,7 @@
       <c r="B11" t="s">
         <v>3</v>
       </c>
+      <c r="C11" s="6"/>
     </row>
     <row r="12" ht="14.25">
       <c r="A12" s="3" t="s">
@@ -825,6 +882,7 @@
       <c r="B12" t="s">
         <v>11</v>
       </c>
+      <c r="C12" s="5"/>
     </row>
     <row r="13" ht="14.25">
       <c r="A13" s="3" t="s">
@@ -833,6 +891,7 @@
       <c r="B13" t="s">
         <v>11</v>
       </c>
+      <c r="C13" s="5"/>
     </row>
     <row r="14" ht="14.25">
       <c r="A14" s="3" t="s">
@@ -841,6 +900,7 @@
       <c r="B14" t="s">
         <v>11</v>
       </c>
+      <c r="C14" s="5"/>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="3" t="s">
@@ -849,6 +909,7 @@
       <c r="B15" t="s">
         <v>3</v>
       </c>
+      <c r="C15" s="4"/>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="3" t="s">
@@ -857,6 +918,7 @@
       <c r="B16" t="s">
         <v>3</v>
       </c>
+      <c r="C16" s="4"/>
     </row>
     <row r="17" ht="14.25">
       <c r="A17" s="3" t="s">
@@ -865,6 +927,7 @@
       <c r="B17" t="s">
         <v>11</v>
       </c>
+      <c r="C17" s="5"/>
     </row>
     <row r="18" ht="14.25">
       <c r="A18" s="3" t="s">
@@ -873,6 +936,7 @@
       <c r="B18" t="s">
         <v>3</v>
       </c>
+      <c r="C18" s="4"/>
     </row>
     <row r="19" ht="14.25">
       <c r="A19" s="3" t="s">
@@ -881,6 +945,7 @@
       <c r="B19" t="s">
         <v>3</v>
       </c>
+      <c r="C19" s="4"/>
     </row>
     <row r="20" ht="14.25">
       <c r="A20" s="3" t="s">
@@ -889,6 +954,7 @@
       <c r="B20" t="s">
         <v>3</v>
       </c>
+      <c r="C20" s="4"/>
     </row>
     <row r="21" ht="14.25">
       <c r="A21" s="3" t="s">
@@ -897,14 +963,16 @@
       <c r="B21" t="s">
         <v>3</v>
       </c>
+      <c r="C21" s="4"/>
     </row>
     <row r="22" ht="14.25">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="7" t="s">
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>3</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C22" s="5"/>
     </row>
     <row r="23" ht="14.25">
       <c r="A23" s="3" t="s">
@@ -913,6 +981,7 @@
       <c r="B23" t="s">
         <v>3</v>
       </c>
+      <c r="C23" s="4"/>
     </row>
     <row r="24" ht="14.25">
       <c r="A24" s="3" t="s">
@@ -921,6 +990,7 @@
       <c r="B24" t="s">
         <v>11</v>
       </c>
+      <c r="C24" s="5"/>
     </row>
     <row r="25" ht="14.25">
       <c r="A25" s="3" t="s">
@@ -929,46 +999,52 @@
       <c r="B25" t="s">
         <v>3</v>
       </c>
+      <c r="C25" s="4"/>
     </row>
     <row r="26" ht="14.25">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B26" t="s">
         <v>11</v>
       </c>
+      <c r="C26" s="5"/>
     </row>
     <row r="27" ht="14.25">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B27" t="s">
         <v>11</v>
       </c>
+      <c r="C27" s="5"/>
     </row>
     <row r="28" ht="14.25">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B28" t="s">
         <v>11</v>
       </c>
+      <c r="C28" s="5"/>
     </row>
     <row r="29" ht="14.25">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B29" t="s">
         <v>3</v>
       </c>
+      <c r="C29" s="4"/>
     </row>
     <row r="30" ht="14.25">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B30" t="s">
         <v>11</v>
       </c>
+      <c r="C30" s="5"/>
     </row>
     <row r="31" ht="14.25"/>
     <row r="32" ht="14.25"/>
